--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R30533e511e974430"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0b9d4ed7e74142ab"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0b9d4ed7e74142ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re1ee3a5a07f2430b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re1ee3a5a07f2430b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R26e29db4764c4670"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R26e29db4764c4670"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8e242b0db14747d1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8e242b0db14747d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8b2556f870f8488e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8b2556f870f8488e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1413178c66d04a5e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1413178c66d04a5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc0eb69dc5a6541a3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc0eb69dc5a6541a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R73c1f87535c74c38"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R73c1f87535c74c38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0f323826b9334635"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0f323826b9334635"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7ba487f8272d4d38"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7ba487f8272d4d38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R99d1f1f686e34943"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R99d1f1f686e34943"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re9fb0a2d1cfb44b8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re9fb0a2d1cfb44b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3706de81fbd74205"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3706de81fbd74205"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rae48988377fd44f5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rae48988377fd44f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd0307659151c4879"/>
   </x:sheets>
 </x:workbook>
 </file>
